--- a/data_group/contrast_PF_SF_evapo.xlsx
+++ b/data_group/contrast_PF_SF_evapo.xlsx
@@ -428,19 +428,19 @@
         </is>
       </c>
       <c r="D2">
-        <v>-102.0427635221984</v>
+        <v>-102.9662347738582</v>
       </c>
       <c r="E2">
-        <v>6.953184440353621</v>
+        <v>4.536306635957888</v>
       </c>
       <c r="F2">
-        <v>701.9345782231576</v>
+        <v>662</v>
       </c>
       <c r="G2">
-        <v>14.67568772230192</v>
+        <v>22.6982527939529</v>
       </c>
       <c r="H2">
-        <v>6.027756606967542E-42</v>
+        <v>1.668137325323924E-84</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="D3">
-        <v>-101.2800245948897</v>
+        <v>-101.9884100318017</v>
       </c>
       <c r="E3">
-        <v>6.953184440353621</v>
+        <v>3.725260541635757</v>
       </c>
       <c r="F3">
-        <v>701.9345782323891</v>
+        <v>662</v>
       </c>
       <c r="G3">
-        <v>14.56599137613828</v>
+        <v>27.37752403943771</v>
       </c>
       <c r="H3">
-        <v>1.036406607551581E-41</v>
+        <v>1.828227768903691E-110</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="D4">
-        <v>-95.82419048025268</v>
+        <v>-95.71885460560057</v>
       </c>
       <c r="E4">
-        <v>7.799457325440187</v>
+        <v>3.027780467947079</v>
       </c>
       <c r="F4">
-        <v>702.1267987820755</v>
+        <v>662</v>
       </c>
       <c r="G4">
-        <v>12.2860074081942</v>
+        <v>31.61353857021895</v>
       </c>
       <c r="H4">
-        <v>2.905679539643708E-31</v>
+        <v>1.273783411438085E-133</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -569,19 +569,19 @@
         </is>
       </c>
       <c r="D5">
-        <v>-72.88533224381757</v>
+        <v>-73.83541839260602</v>
       </c>
       <c r="E5">
-        <v>6.953184440353622</v>
+        <v>4.56025391483563</v>
       </c>
       <c r="F5">
-        <v>701.9345782447261</v>
+        <v>662</v>
       </c>
       <c r="G5">
-        <v>10.48229525177255</v>
+        <v>16.19107614872084</v>
       </c>
       <c r="H5">
-        <v>3.313719688136415E-23</v>
+        <v>1.280639383432038E-49</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="D6">
-        <v>-68.43640071884569</v>
+        <v>-68.05160111792108</v>
       </c>
       <c r="E6">
-        <v>6.953184440353622</v>
+        <v>3.678565163876885</v>
       </c>
       <c r="F6">
-        <v>701.9345782476233</v>
+        <v>662</v>
       </c>
       <c r="G6">
-        <v>9.842454389914785</v>
+        <v>18.49949588665181</v>
       </c>
       <c r="H6">
-        <v>5.059341731040739E-21</v>
+        <v>1.986023692522443E-61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="D7">
-        <v>-62.13064276030224</v>
+        <v>-61.79268805894068</v>
       </c>
       <c r="E7">
-        <v>7.799457325440187</v>
+        <v>3.220943070874427</v>
       </c>
       <c r="F7">
-        <v>702.1267987914194</v>
+        <v>662</v>
       </c>
       <c r="G7">
-        <v>7.966021245817343</v>
+        <v>19.18465700859627</v>
       </c>
       <c r="H7">
-        <v>1.323470145429818E-14</v>
+        <v>8.700647163520827E-65</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -710,19 +710,19 @@
         </is>
       </c>
       <c r="D8">
-        <v>-51.24079465329632</v>
+        <v>-51.46946849366543</v>
       </c>
       <c r="E8">
-        <v>6.953184440353628</v>
+        <v>4.797542144217438</v>
       </c>
       <c r="F8">
-        <v>701.9345782418534</v>
+        <v>662</v>
       </c>
       <c r="G8">
-        <v>7.369399602851654</v>
+        <v>10.72829939716163</v>
       </c>
       <c r="H8">
-        <v>2.898419497417998E-12</v>
+        <v>1.446111271715996E-24</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="D9">
-        <v>-50.41504175750357</v>
+        <v>-50.45330265086554</v>
       </c>
       <c r="E9">
-        <v>6.953184440353628</v>
+        <v>4.037757939859128</v>
       </c>
       <c r="F9">
-        <v>701.9345782457523</v>
+        <v>662</v>
       </c>
       <c r="G9">
-        <v>7.250640651053914</v>
+        <v>12.49537575118378</v>
       </c>
       <c r="H9">
-        <v>3.294560042315392E-12</v>
+        <v>7.663592247644255E-32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="D10">
-        <v>-47.91982953045231</v>
+        <v>-46.55080530017241</v>
       </c>
       <c r="E10">
-        <v>7.799457325440192</v>
+        <v>3.67992794437111</v>
       </c>
       <c r="F10">
-        <v>702.126798797882</v>
+        <v>662</v>
       </c>
       <c r="G10">
-        <v>6.143995348772266</v>
+        <v>12.64992304302519</v>
       </c>
       <c r="H10">
-        <v>2.69570074189083E-09</v>
+        <v>3.162389392477198E-32</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="D11">
-        <v>-46.59660287670987</v>
+        <v>-46.29719359518676</v>
       </c>
       <c r="E11">
-        <v>6.953184440353623</v>
+        <v>5.301862487602397</v>
       </c>
       <c r="F11">
-        <v>701.934578235106</v>
+        <v>662</v>
       </c>
       <c r="G11">
-        <v>6.701476607794409</v>
+        <v>8.732250921906356</v>
       </c>
       <c r="H11">
-        <v>2.542758083457521E-10</v>
+        <v>4.055739558433477E-17</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -898,19 +898,19 @@
         </is>
       </c>
       <c r="D12">
-        <v>-42.76493124125388</v>
+        <v>-41.96178152964959</v>
       </c>
       <c r="E12">
-        <v>6.953184440353623</v>
+        <v>4.140527937248927</v>
       </c>
       <c r="F12">
-        <v>701.9345782358981</v>
+        <v>662</v>
       </c>
       <c r="G12">
-        <v>6.15040944305498</v>
+        <v>10.13440367160765</v>
       </c>
       <c r="H12">
-        <v>3.891925578846139E-09</v>
+        <v>9.302911027651244E-22</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D13">
-        <v>-38.89680002247533</v>
+        <v>-38.2911234982588</v>
       </c>
       <c r="E13">
-        <v>7.799457325440187</v>
+        <v>3.995411969215711</v>
       </c>
       <c r="F13">
-        <v>702.1267987887554</v>
+        <v>662</v>
       </c>
       <c r="G13">
-        <v>4.987116205585504</v>
+        <v>9.583773536568557</v>
       </c>
       <c r="H13">
-        <v>1.546309177929931E-06</v>
+        <v>5.545050963881208E-20</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="D14">
-        <v>-41.79990706953793</v>
+        <v>-41.47434479908769</v>
       </c>
       <c r="E14">
-        <v>6.953184440353628</v>
+        <v>5.773864011775178</v>
       </c>
       <c r="F14">
-        <v>701.9345782567642</v>
+        <v>662</v>
       </c>
       <c r="G14">
-        <v>6.011620636286768</v>
+        <v>7.18311770324088</v>
       </c>
       <c r="H14">
-        <v>8.857188456165532E-09</v>
+        <v>3.679418624701826E-12</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1039,19 +1039,19 @@
         </is>
       </c>
       <c r="D15">
-        <v>-43.7902223968178</v>
+        <v>-42.0816436049147</v>
       </c>
       <c r="E15">
-        <v>6.953184440353628</v>
+        <v>4.172350889909947</v>
       </c>
       <c r="F15">
-        <v>701.9345782500733</v>
+        <v>662</v>
       </c>
       <c r="G15">
-        <v>6.297865786886951</v>
+        <v>10.08583523180692</v>
       </c>
       <c r="H15">
-        <v>3.192826462596526E-09</v>
+        <v>1.429279588559717E-21</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1086,19 +1086,19 @@
         </is>
       </c>
       <c r="D16">
-        <v>-33.91080775086081</v>
+        <v>-34.10854879391656</v>
       </c>
       <c r="E16">
-        <v>7.799457325440192</v>
+        <v>3.877024784944225</v>
       </c>
       <c r="F16">
-        <v>702.1267988014837</v>
+        <v>662</v>
       </c>
       <c r="G16">
-        <v>4.347841950522747</v>
+        <v>8.797609168342536</v>
       </c>
       <c r="H16">
-        <v>3.156668575899521E-05</v>
+        <v>3.6175820133705E-17</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="D17">
-        <v>-37.68305794507737</v>
+        <v>-36.08392258428697</v>
       </c>
       <c r="E17">
-        <v>6.953184440353628</v>
+        <v>6.279698474638031</v>
       </c>
       <c r="F17">
-        <v>701.9345782571612</v>
+        <v>662</v>
       </c>
       <c r="G17">
-        <v>5.419539531610767</v>
+        <v>5.746123437298777</v>
       </c>
       <c r="H17">
-        <v>4.93306688634032E-07</v>
+        <v>2.786546307497632E-08</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="D18">
-        <v>-34.69070832018841</v>
+        <v>-35.12210332430467</v>
       </c>
       <c r="E18">
-        <v>6.953184440353628</v>
+        <v>4.199286600326767</v>
       </c>
       <c r="F18">
-        <v>701.9345782501357</v>
+        <v>662</v>
       </c>
       <c r="G18">
-        <v>4.989182815122347</v>
+        <v>8.363826208378265</v>
       </c>
       <c r="H18">
-        <v>2.295774930251301E-06</v>
+        <v>1.077116062050118E-15</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1227,19 +1227,19 @@
         </is>
       </c>
       <c r="D19">
-        <v>-35.83615238334784</v>
+        <v>-35.7363172881177</v>
       </c>
       <c r="E19">
-        <v>7.799457325440192</v>
+        <v>4.039773581568391</v>
       </c>
       <c r="F19">
-        <v>702.1267988016209</v>
+        <v>662</v>
       </c>
       <c r="G19">
-        <v>4.594698180661601</v>
+        <v>8.846118864474461</v>
       </c>
       <c r="H19">
-        <v>1.027504774732521E-05</v>
+        <v>4.909818781177526E-17</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="D20">
-        <v>-42.4932535811984</v>
+        <v>-37.04797650461965</v>
       </c>
       <c r="E20">
-        <v>6.953184440353624</v>
+        <v>10.39168282762733</v>
       </c>
       <c r="F20">
-        <v>701.9345782354312</v>
+        <v>662</v>
       </c>
       <c r="G20">
-        <v>6.111337034953913</v>
+        <v>3.565156589087178</v>
       </c>
       <c r="H20">
-        <v>9.827379349249398E-09</v>
+        <v>0.0007796381921214346</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="D21">
-        <v>-27.34377104764952</v>
+        <v>-25.78990149468353</v>
       </c>
       <c r="E21">
-        <v>6.953184440353624</v>
+        <v>5.294520388772854</v>
       </c>
       <c r="F21">
-        <v>701.9345782359809</v>
+        <v>662</v>
       </c>
       <c r="G21">
-        <v>3.9325536784206</v>
+        <v>4.871055279978066</v>
       </c>
       <c r="H21">
-        <v>0.0001847774559236687</v>
+        <v>4.170309265541593E-06</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="D22">
-        <v>-36.9641577444625</v>
+        <v>-35.26862398029284</v>
       </c>
       <c r="E22">
-        <v>7.799457325440188</v>
+        <v>4.951861665876828</v>
       </c>
       <c r="F22">
-        <v>702.1267987887343</v>
+        <v>662</v>
       </c>
       <c r="G22">
-        <v>4.739324314769081</v>
+        <v>7.122295887893672</v>
       </c>
       <c r="H22">
-        <v>7.789771977778753E-06</v>
+        <v>1.66562940957191E-11</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1415,19 +1415,19 @@
         </is>
       </c>
       <c r="D23">
-        <v>-32.88813749057149</v>
+        <v>-46.66522779206137</v>
       </c>
       <c r="E23">
-        <v>6.953184440353626</v>
+        <v>11.98599243341198</v>
       </c>
       <c r="F23">
-        <v>701.9345782423754</v>
+        <v>662</v>
       </c>
       <c r="G23">
-        <v>4.729938889539778</v>
+        <v>3.893313636839786</v>
       </c>
       <c r="H23">
-        <v>8.147399442195583E-06</v>
+        <v>0.0002178131519240734</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1462,19 +1462,19 @@
         </is>
       </c>
       <c r="D24">
-        <v>-46.37344083397095</v>
+        <v>-37.82224324942239</v>
       </c>
       <c r="E24">
-        <v>6.953184440353626</v>
+        <v>6.720704307717734</v>
       </c>
       <c r="F24">
-        <v>701.9345782457856</v>
+        <v>662</v>
       </c>
       <c r="G24">
-        <v>6.669381667029745</v>
+        <v>5.627720178968318</v>
       </c>
       <c r="H24">
-        <v>3.124558176626637E-10</v>
+        <v>1.618570592523386E-07</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1509,19 +1509,19 @@
         </is>
       </c>
       <c r="D25">
-        <v>-32.19727456742472</v>
+        <v>-31.29747236132735</v>
       </c>
       <c r="E25">
-        <v>7.79945732544019</v>
+        <v>5.710579772166779</v>
       </c>
       <c r="F25">
-        <v>702.1267987978356</v>
+        <v>662</v>
       </c>
       <c r="G25">
-        <v>4.128142923790862</v>
+        <v>5.480612058668796</v>
       </c>
       <c r="H25">
-        <v>8.193295992316824E-05</v>
+        <v>1.809218490386479E-07</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="D26">
-        <v>-38.7168869824663</v>
+        <v>-44.6852703742296</v>
       </c>
       <c r="E26">
-        <v>7.13851633883742</v>
+        <v>13.77475174434454</v>
       </c>
       <c r="F26">
-        <v>701.9657367178758</v>
+        <v>662</v>
       </c>
       <c r="G26">
-        <v>5.423660203987393</v>
+        <v>3.243998237033629</v>
       </c>
       <c r="H26">
-        <v>4.825041580571785E-07</v>
+        <v>0.002475825538276087</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="D27">
-        <v>-28.77912219197598</v>
+        <v>-27.65491471530858</v>
       </c>
       <c r="E27">
-        <v>6.953184440353619</v>
+        <v>6.76307764613347</v>
       </c>
       <c r="F27">
-        <v>701.9345782471441</v>
+        <v>662</v>
       </c>
       <c r="G27">
-        <v>4.138984437828656</v>
+        <v>4.089102057126198</v>
       </c>
       <c r="H27">
-        <v>0.0001173698167381637</v>
+        <v>0.0001459011224438118</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1650,19 +1650,19 @@
         </is>
       </c>
       <c r="D28">
-        <v>-31.45722908313214</v>
+        <v>-35.30389209407777</v>
       </c>
       <c r="E28">
-        <v>7.799457325440184</v>
+        <v>6.661982562788341</v>
       </c>
       <c r="F28">
-        <v>702.1267987910715</v>
+        <v>662</v>
       </c>
       <c r="G28">
-        <v>4.033258696156373</v>
+        <v>5.299307189915774</v>
       </c>
       <c r="H28">
-        <v>0.0001220760904727966</v>
+        <v>9.510636330591515E-07</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1697,19 +1697,19 @@
         </is>
       </c>
       <c r="D29">
-        <v>-36.56172930516323</v>
+        <v>-30.31476302584241</v>
       </c>
       <c r="E29">
-        <v>7.634030368392398</v>
+        <v>10.71814310144431</v>
       </c>
       <c r="F29">
-        <v>702.0452006700153</v>
+        <v>662</v>
       </c>
       <c r="G29">
-        <v>4.789308863184746</v>
+        <v>2.828359608462157</v>
       </c>
       <c r="H29">
-        <v>6.127297602689334E-06</v>
+        <v>0.009640499416381423</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="D30">
-        <v>-7.239769947704185</v>
+        <v>0.8769522466466952</v>
       </c>
       <c r="E30">
-        <v>6.95318444035362</v>
+        <v>6.931904162561345</v>
       </c>
       <c r="F30">
-        <v>701.9345782329418</v>
+        <v>662</v>
       </c>
       <c r="G30">
-        <v>1.041216439720386</v>
+        <v>-0.1265095745816919</v>
       </c>
       <c r="H30">
-        <v>0.2981335955914861</v>
+        <v>0.8993669839192155</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="D31">
-        <v>16.15581761402759</v>
+        <v>13.24690280835958</v>
       </c>
       <c r="E31">
-        <v>7.799457325440186</v>
+        <v>6.02420071484683</v>
       </c>
       <c r="F31">
-        <v>702.1267987825964</v>
+        <v>662</v>
       </c>
       <c r="G31">
-        <v>-2.071402783541198</v>
+        <v>-2.198947783348615</v>
       </c>
       <c r="H31">
-        <v>0.0464230421027701</v>
+        <v>0.04164878422608042</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1833,19 +1833,19 @@
         </is>
       </c>
       <c r="D32">
-        <v>-14.28887082458152</v>
+        <v>-14.77039527978149</v>
       </c>
       <c r="E32">
-        <v>5.591043280319656</v>
+        <v>5.58999341308308</v>
       </c>
       <c r="F32">
-        <v>710.0121662369107</v>
+        <v>670</v>
       </c>
       <c r="G32">
-        <v>2.555671653424328</v>
+        <v>2.64229207233271</v>
       </c>
       <c r="H32">
-        <v>0.03241653636100154</v>
+        <v>0.02528100940018764</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1880,19 +1880,19 @@
         </is>
       </c>
       <c r="D33">
-        <v>-14.3556882526671</v>
+        <v>-14.58028264813596</v>
       </c>
       <c r="E33">
-        <v>5.591043280319656</v>
+        <v>5.221152227873174</v>
       </c>
       <c r="F33">
-        <v>710.0121662385244</v>
+        <v>670</v>
       </c>
       <c r="G33">
-        <v>2.567622451287185</v>
+        <v>2.792541188571168</v>
       </c>
       <c r="H33">
-        <v>0.03241653636100154</v>
+        <v>0.02528100940018764</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1927,19 +1927,19 @@
         </is>
       </c>
       <c r="D34">
-        <v>-8.966441685806727</v>
+        <v>-9.442110441138604</v>
       </c>
       <c r="E34">
-        <v>6.271480876673278</v>
+        <v>4.667512734930246</v>
       </c>
       <c r="F34">
-        <v>710.1462987643866</v>
+        <v>670</v>
       </c>
       <c r="G34">
-        <v>1.42971681842439</v>
+        <v>2.022942620054729</v>
       </c>
       <c r="H34">
-        <v>0.3064761715641445</v>
+        <v>0.08695143927513031</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="D35">
-        <v>-17.68083458565447</v>
+        <v>-18.47602032848597</v>
       </c>
       <c r="E35">
-        <v>5.591043280319653</v>
+        <v>5.535143931627514</v>
       </c>
       <c r="F35">
-        <v>710.0121662368178</v>
+        <v>670</v>
       </c>
       <c r="G35">
-        <v>3.162349797557571</v>
+        <v>3.337947586677013</v>
       </c>
       <c r="H35">
-        <v>0.009789841985211691</v>
+        <v>0.005344147069059571</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="D36">
-        <v>-13.20695006295286</v>
+        <v>-14.08554308428292</v>
       </c>
       <c r="E36">
-        <v>5.591043280319653</v>
+        <v>5.010908735420566</v>
       </c>
       <c r="F36">
-        <v>710.0121662381783</v>
+        <v>670</v>
       </c>
       <c r="G36">
-        <v>2.3621620153507</v>
+        <v>2.810975778648006</v>
       </c>
       <c r="H36">
-        <v>0.05531271876624237</v>
+        <v>0.01016695097006928</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2038,6 +2038,11 @@
       <c r="J36" t="inlineStr">
         <is>
           <t>SF_intermediate</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -2058,19 +2063,19 @@
         </is>
       </c>
       <c r="D37">
-        <v>-7.804073772272538</v>
+        <v>-7.890486571102846</v>
       </c>
       <c r="E37">
-        <v>6.271480876673275</v>
+        <v>4.613376298344892</v>
       </c>
       <c r="F37">
-        <v>710.1462987640696</v>
+        <v>670</v>
       </c>
       <c r="G37">
-        <v>1.244374961151477</v>
+        <v>1.710349657350444</v>
       </c>
       <c r="H37">
-        <v>0.3206581974532823</v>
+        <v>0.1051970100617523</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2100,19 +2105,19 @@
         </is>
       </c>
       <c r="D38">
-        <v>-20.8698690530465</v>
+        <v>-21.88383469864152</v>
       </c>
       <c r="E38">
-        <v>5.591043280319661</v>
+        <v>5.23666964092858</v>
       </c>
       <c r="F38">
-        <v>710.0121662355565</v>
+        <v>670</v>
       </c>
       <c r="G38">
-        <v>3.732732516399568</v>
+        <v>4.178960331505851</v>
       </c>
       <c r="H38">
-        <v>0.001227414544106152</v>
+        <v>0.0001989967230596708</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2147,19 +2152,19 @@
         </is>
       </c>
       <c r="D39">
-        <v>-17.06564720633364</v>
+        <v>-18.05647503131932</v>
       </c>
       <c r="E39">
-        <v>5.591043280319661</v>
+        <v>4.736308810237764</v>
       </c>
       <c r="F39">
-        <v>710.0121662379312</v>
+        <v>670</v>
       </c>
       <c r="G39">
-        <v>3.052318923447492</v>
+        <v>3.812351718344327</v>
       </c>
       <c r="H39">
-        <v>0.007066615364349586</v>
+        <v>0.0004510254962834861</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2194,19 +2199,19 @@
         </is>
       </c>
       <c r="D40">
-        <v>-13.76653216341754</v>
+        <v>-13.42129077836541</v>
       </c>
       <c r="E40">
-        <v>6.271480876673282</v>
+        <v>4.308112353505209</v>
       </c>
       <c r="F40">
-        <v>710.1462987633364</v>
+        <v>670</v>
       </c>
       <c r="G40">
-        <v>2.195100716103917</v>
+        <v>3.115353007784359</v>
       </c>
       <c r="H40">
-        <v>0.05695861731522315</v>
+        <v>0.003831367031650247</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2216,6 +2221,11 @@
       <c r="J40" t="inlineStr">
         <is>
           <t>SF_advanced</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -2236,19 +2246,19 @@
         </is>
       </c>
       <c r="D41">
-        <v>-29.57657834632282</v>
+        <v>-30.4082861375322</v>
       </c>
       <c r="E41">
-        <v>5.591043280319656</v>
+        <v>4.526626735413715</v>
       </c>
       <c r="F41">
-        <v>710.0121662354414</v>
+        <v>670</v>
       </c>
       <c r="G41">
-        <v>5.289992737210906</v>
+        <v>6.717648243367478</v>
       </c>
       <c r="H41">
-        <v>9.786403940246711E-07</v>
+        <v>2.368566473685747E-10</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2283,19 +2293,19 @@
         </is>
       </c>
       <c r="D42">
-        <v>-23.48561395568678</v>
+        <v>-23.8920700460593</v>
       </c>
       <c r="E42">
-        <v>5.591043280319656</v>
+        <v>3.964605467751809</v>
       </c>
       <c r="F42">
-        <v>710.012166237755</v>
+        <v>670</v>
       </c>
       <c r="G42">
-        <v>4.200578099324612</v>
+        <v>6.026342404155455</v>
       </c>
       <c r="H42">
-        <v>9.004232524126318E-05</v>
+        <v>8.304653462220194E-09</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2330,19 +2340,19 @@
         </is>
       </c>
       <c r="D43">
-        <v>-21.28585095898412</v>
+        <v>-21.43062558881142</v>
       </c>
       <c r="E43">
-        <v>6.271480876673277</v>
+        <v>3.648887157584604</v>
       </c>
       <c r="F43">
-        <v>710.1462987620827</v>
+        <v>670</v>
       </c>
       <c r="G43">
-        <v>3.394070934371605</v>
+        <v>5.873194939521645</v>
       </c>
       <c r="H43">
-        <v>0.001453741012123786</v>
+        <v>1.346344645456174E-08</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2377,19 +2387,19 @@
         </is>
       </c>
       <c r="D44">
-        <v>-42.04959814478947</v>
+        <v>-42.52475820484927</v>
       </c>
       <c r="E44">
-        <v>5.591043280319659</v>
+        <v>3.978958647352958</v>
       </c>
       <c r="F44">
-        <v>710.0121662348915</v>
+        <v>670</v>
       </c>
       <c r="G44">
-        <v>7.520885823367361</v>
+        <v>10.68740893629022</v>
       </c>
       <c r="H44">
-        <v>9.886461841561594E-13</v>
+        <v>3.011083743576226E-24</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2424,19 +2434,19 @@
         </is>
       </c>
       <c r="D45">
-        <v>-38.78688950101418</v>
+        <v>-38.37666152162475</v>
       </c>
       <c r="E45">
-        <v>5.591043280319659</v>
+        <v>3.394758625304468</v>
       </c>
       <c r="F45">
-        <v>710.012166238207</v>
+        <v>670</v>
       </c>
       <c r="G45">
-        <v>6.937325925832683</v>
+        <v>11.30468046698986</v>
       </c>
       <c r="H45">
-        <v>2.702693789221058E-11</v>
+        <v>1.830537811851752E-26</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2471,19 +2481,19 @@
         </is>
       </c>
       <c r="D46">
-        <v>-33.97825543651972</v>
+        <v>-34.64204175773537</v>
       </c>
       <c r="E46">
-        <v>6.27148087667328</v>
+        <v>3.326871431177077</v>
       </c>
       <c r="F46">
-        <v>710.1462987640235</v>
+        <v>670</v>
       </c>
       <c r="G46">
-        <v>5.417899871607926</v>
+        <v>10.41279847279181</v>
       </c>
       <c r="H46">
-        <v>1.65294715704233E-07</v>
+        <v>2.4608703571392E-23</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2518,19 +2528,19 @@
         </is>
       </c>
       <c r="D47">
-        <v>-64.02097331651854</v>
+        <v>-63.725557725382</v>
       </c>
       <c r="E47">
-        <v>5.591043280319661</v>
+        <v>4.443154345519046</v>
       </c>
       <c r="F47">
-        <v>710.0121662348915</v>
+        <v>670</v>
       </c>
       <c r="G47">
-        <v>11.45063096575747</v>
+        <v>14.34241369302187</v>
       </c>
       <c r="H47">
-        <v>3.367644185924714E-27</v>
+        <v>4.21291368876514E-40</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2565,19 +2575,19 @@
         </is>
       </c>
       <c r="D48">
-        <v>-58.92360617815198</v>
+        <v>-57.77914690782819</v>
       </c>
       <c r="E48">
-        <v>5.591043280319661</v>
+        <v>4.336784767920239</v>
       </c>
       <c r="F48">
-        <v>710.0121662382071</v>
+        <v>670</v>
       </c>
       <c r="G48">
-        <v>10.53892864424099</v>
+        <v>13.32303768801903</v>
       </c>
       <c r="H48">
-        <v>9.45720722735241E-24</v>
+        <v>8.600362888246558E-36</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2612,19 +2622,19 @@
         </is>
       </c>
       <c r="D49">
-        <v>-55.53424027504195</v>
+        <v>-56.51951580919476</v>
       </c>
       <c r="E49">
-        <v>6.271480876673282</v>
+        <v>4.10956269016079</v>
       </c>
       <c r="F49">
-        <v>710.1462987639807</v>
+        <v>670</v>
       </c>
       <c r="G49">
-        <v>8.855044186071119</v>
+        <v>13.753170366403</v>
       </c>
       <c r="H49">
-        <v>1.324949079287971E-17</v>
+        <v>1.300861220999092E-37</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2659,19 +2669,19 @@
         </is>
       </c>
       <c r="D50">
-        <v>-79.94666625533587</v>
+        <v>-80.11543997218655</v>
       </c>
       <c r="E50">
-        <v>5.591043280319655</v>
+        <v>5.642872335334257</v>
       </c>
       <c r="F50">
-        <v>710.0121662354413</v>
+        <v>670</v>
       </c>
       <c r="G50">
-        <v>14.29906052359607</v>
+        <v>14.1976346816361</v>
       </c>
       <c r="H50">
-        <v>3.631830957764914E-40</v>
+        <v>2.070286000109595E-39</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2706,19 +2716,19 @@
         </is>
       </c>
       <c r="D51">
-        <v>-68.880702776234</v>
+        <v>-66.88671037203184</v>
       </c>
       <c r="E51">
-        <v>5.591043280319655</v>
+        <v>5.251259612311992</v>
       </c>
       <c r="F51">
-        <v>710.0121662377549</v>
+        <v>670</v>
       </c>
       <c r="G51">
-        <v>12.31983000716387</v>
+        <v>12.73726978098944</v>
       </c>
       <c r="H51">
-        <v>2.876238797272437E-31</v>
+        <v>3.929288700726426E-33</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2753,19 +2763,19 @@
         </is>
       </c>
       <c r="D52">
-        <v>-66.82605095632542</v>
+        <v>-68.43124136417848</v>
       </c>
       <c r="E52">
-        <v>6.271480876673277</v>
+        <v>5.362627706662829</v>
       </c>
       <c r="F52">
-        <v>710.1462987620417</v>
+        <v>670</v>
       </c>
       <c r="G52">
-        <v>10.65554567899336</v>
+        <v>12.7607667560356</v>
       </c>
       <c r="H52">
-        <v>2.14736182394343E-24</v>
+        <v>3.929288700726426E-33</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2800,19 +2810,19 @@
         </is>
       </c>
       <c r="D53">
-        <v>-97.5164523744553</v>
+        <v>-96.96496931791383</v>
       </c>
       <c r="E53">
-        <v>5.591043280319658</v>
+        <v>6.224446505561203</v>
       </c>
       <c r="F53">
-        <v>710.0121662355562</v>
+        <v>670</v>
       </c>
       <c r="G53">
-        <v>17.44154847051729</v>
+        <v>15.57808702047337</v>
       </c>
       <c r="H53">
-        <v>3.43479602914894E-56</v>
+        <v>3.816197511920655E-46</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2847,19 +2857,19 @@
         </is>
       </c>
       <c r="D54">
-        <v>-79.69135353071216</v>
+        <v>-75.97975854851148</v>
       </c>
       <c r="E54">
-        <v>5.591043280319658</v>
+        <v>6.824597654470377</v>
       </c>
       <c r="F54">
-        <v>710.0121662379312</v>
+        <v>670</v>
       </c>
       <c r="G54">
-        <v>14.25339592902524</v>
+        <v>11.13322167772657</v>
       </c>
       <c r="H54">
-        <v>3.020929389887681E-40</v>
+        <v>3.120502615205334E-26</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2894,19 +2904,19 @@
         </is>
       </c>
       <c r="D55">
-        <v>-71.18291744920803</v>
+        <v>-74.24933344953691</v>
       </c>
       <c r="E55">
-        <v>6.27148087667328</v>
+        <v>6.6326127716145</v>
       </c>
       <c r="F55">
-        <v>710.1462987633685</v>
+        <v>670</v>
       </c>
       <c r="G55">
-        <v>11.35025663778587</v>
+        <v>11.19458289006419</v>
       </c>
       <c r="H55">
-        <v>2.972094561007589E-27</v>
+        <v>2.615150926957549E-26</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2941,19 +2951,19 @@
         </is>
       </c>
       <c r="D56">
-        <v>-99.34819672778532</v>
+        <v>-99.8049877294257</v>
       </c>
       <c r="E56">
-        <v>5.591043280319655</v>
+        <v>7.934957401188389</v>
       </c>
       <c r="F56">
-        <v>710.0121662368178</v>
+        <v>670</v>
       </c>
       <c r="G56">
-        <v>17.76916967849072</v>
+        <v>12.57788576337893</v>
       </c>
       <c r="H56">
-        <v>6.117952960540615E-58</v>
+        <v>6.06528991184246E-32</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2988,19 +2998,19 @@
         </is>
       </c>
       <c r="D57">
-        <v>-96.25001433684217</v>
+        <v>-91.74463001224294</v>
       </c>
       <c r="E57">
-        <v>5.591043280319656</v>
+        <v>8.799302510909806</v>
       </c>
       <c r="F57">
-        <v>710.0121662381781</v>
+        <v>670</v>
       </c>
       <c r="G57">
-        <v>17.21503653453015</v>
+        <v>10.42635253174822</v>
       </c>
       <c r="H57">
-        <v>2.73405856661156E-55</v>
+        <v>3.265293363628874E-23</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3035,19 +3045,19 @@
         </is>
       </c>
       <c r="D58">
-        <v>-74.18649468139854</v>
+        <v>-78.26524202848698</v>
       </c>
       <c r="E58">
-        <v>6.271480876673277</v>
+        <v>8.100228553169268</v>
       </c>
       <c r="F58">
-        <v>710.1462987641065</v>
+        <v>670</v>
       </c>
       <c r="G58">
-        <v>11.82918295379559</v>
+        <v>9.662102928918616</v>
       </c>
       <c r="H58">
-        <v>2.698743580911204E-29</v>
+        <v>1.832187467685125E-20</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3082,19 +3092,19 @@
         </is>
       </c>
       <c r="D59">
-        <v>-120.6130645549569</v>
+        <v>-120.0880646866332</v>
       </c>
       <c r="E59">
-        <v>5.591043280319655</v>
+        <v>11.62314900977641</v>
       </c>
       <c r="F59">
-        <v>710.0121662369108</v>
+        <v>670</v>
       </c>
       <c r="G59">
-        <v>21.57255068647243</v>
+        <v>10.33180118276255</v>
       </c>
       <c r="H59">
-        <v>5.47475789286638E-79</v>
+        <v>1.532685427282206E-22</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3129,19 +3139,19 @@
         </is>
       </c>
       <c r="D60">
-        <v>-97.82589170026748</v>
+        <v>-90.63969240512102</v>
       </c>
       <c r="E60">
-        <v>5.591043280319655</v>
+        <v>10.45485412417445</v>
       </c>
       <c r="F60">
-        <v>710.0121662385244</v>
+        <v>670</v>
       </c>
       <c r="G60">
-        <v>17.49689401343259</v>
+        <v>8.669627651287598</v>
       </c>
       <c r="H60">
-        <v>8.714587754699361E-57</v>
+        <v>9.758722015433332E-17</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3176,19 +3186,19 @@
         </is>
       </c>
       <c r="D61">
-        <v>-79.13354102604652</v>
+        <v>-84.8548890848335</v>
       </c>
       <c r="E61">
-        <v>6.271480876673277</v>
+        <v>10.68614808350094</v>
       </c>
       <c r="F61">
-        <v>710.1462987642573</v>
+        <v>670</v>
       </c>
       <c r="G61">
-        <v>12.61799925443177</v>
+        <v>7.940643197322582</v>
       </c>
       <c r="H61">
-        <v>8.896372859110196E-33</v>
+        <v>1.69986241876215E-14</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3223,19 +3233,19 @@
         </is>
       </c>
       <c r="D62">
-        <v>13.96056616200975</v>
+        <v>15.38107489733548</v>
       </c>
       <c r="E62">
-        <v>7.808558695844055</v>
+        <v>5.265981349446283</v>
       </c>
       <c r="F62">
-        <v>709.9665023179817</v>
+        <v>670</v>
       </c>
       <c r="G62">
-        <v>-1.787854417927341</v>
+        <v>-2.920837328630645</v>
       </c>
       <c r="H62">
-        <v>0.1881688199873937</v>
+        <v>0.007216606144583724</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3245,6 +3255,11 @@
       <c r="J62" t="inlineStr">
         <is>
           <t>SF_early</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -3265,19 +3280,19 @@
         </is>
       </c>
       <c r="D63">
-        <v>14.32579574659691</v>
+        <v>17.4068483361719</v>
       </c>
       <c r="E63">
-        <v>7.808558695844055</v>
+        <v>5.004642034928779</v>
       </c>
       <c r="F63">
-        <v>709.9665023175622</v>
+        <v>670</v>
       </c>
       <c r="G63">
-        <v>-1.834627401113283</v>
+        <v>-3.478140537262145</v>
       </c>
       <c r="H63">
-        <v>0.1881688199873937</v>
+        <v>0.001612707256409289</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3287,6 +3302,11 @@
       <c r="J63" t="inlineStr">
         <is>
           <t>SF_intermediate</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -3307,19 +3327,19 @@
         </is>
       </c>
       <c r="D64">
-        <v>14.68444097838499</v>
+        <v>21.39941349343341</v>
       </c>
       <c r="E64">
-        <v>8.759091211443806</v>
+        <v>4.836580000291286</v>
       </c>
       <c r="F64">
-        <v>710.0297987321383</v>
+        <v>670</v>
       </c>
       <c r="G64">
-        <v>-1.67647997079876</v>
+        <v>-4.424492821817197</v>
       </c>
       <c r="H64">
-        <v>0.1881688199873937</v>
+        <v>6.768561485640673E-05</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3329,6 +3349,11 @@
       <c r="J64" t="inlineStr">
         <is>
           <t>SF_advanced</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -3349,19 +3374,19 @@
         </is>
       </c>
       <c r="D65">
-        <v>-9.745207481897586</v>
+        <v>-6.496145173796897</v>
       </c>
       <c r="E65">
-        <v>7.80855869584405</v>
+        <v>5.819827359893861</v>
       </c>
       <c r="F65">
-        <v>709.9665023187569</v>
+        <v>670</v>
       </c>
       <c r="G65">
-        <v>1.248016165529277</v>
+        <v>1.116209257093044</v>
       </c>
       <c r="H65">
-        <v>0.46805498243021</v>
+        <v>0.3176792699906082</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3391,19 +3416,19 @@
         </is>
       </c>
       <c r="D66">
-        <v>-3.571904734405129</v>
+        <v>-2.230656705838182</v>
       </c>
       <c r="E66">
-        <v>7.80855869584405</v>
+        <v>5.813327623469958</v>
       </c>
       <c r="F66">
-        <v>709.9665023184532</v>
+        <v>670</v>
       </c>
       <c r="G66">
-        <v>0.4574345757695596</v>
+        <v>0.3837142597696411</v>
       </c>
       <c r="H66">
-        <v>0.6474986621402026</v>
+        <v>0.7013119738857935</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3433,19 +3458,19 @@
         </is>
       </c>
       <c r="D67">
-        <v>6.860710657531904</v>
+        <v>11.97598070021122</v>
       </c>
       <c r="E67">
-        <v>8.759091211443801</v>
+        <v>5.543387671033092</v>
       </c>
       <c r="F67">
-        <v>710.0297987320553</v>
+        <v>670</v>
       </c>
       <c r="G67">
-        <v>-0.7832674066195757</v>
+        <v>-2.160408293793264</v>
       </c>
       <c r="H67">
-        <v>0.5204775321473439</v>
+        <v>0.06218984568895492</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3475,19 +3500,19 @@
         </is>
       </c>
       <c r="D68">
-        <v>-9.093692408418613</v>
+        <v>-7.416982119620577</v>
       </c>
       <c r="E68">
-        <v>7.808558695844061</v>
+        <v>6.519104534034753</v>
       </c>
       <c r="F68">
-        <v>709.9665023178005</v>
+        <v>670</v>
       </c>
       <c r="G68">
-        <v>1.16458014374132</v>
+        <v>1.137730202192373</v>
       </c>
       <c r="H68">
-        <v>0.6728517211507835</v>
+        <v>0.306767818587941</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3517,19 +3542,19 @@
         </is>
       </c>
       <c r="D69">
-        <v>-13.63875691290087</v>
+        <v>-13.88357172026727</v>
       </c>
       <c r="E69">
-        <v>7.808558695844061</v>
+        <v>6.76079926080723</v>
       </c>
       <c r="F69">
-        <v>709.9665023174197</v>
+        <v>670</v>
       </c>
       <c r="G69">
-        <v>1.746642042936785</v>
+        <v>2.053540000921369</v>
       </c>
       <c r="H69">
-        <v>0.4867913577538425</v>
+        <v>0.06061178566456607</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3559,19 +3584,19 @@
         </is>
       </c>
       <c r="D70">
-        <v>-7.582721273115352</v>
+        <v>-3.975336150884694</v>
       </c>
       <c r="E70">
-        <v>8.759091211443812</v>
+        <v>6.436017271381783</v>
       </c>
       <c r="F70">
-        <v>710.0297987318293</v>
+        <v>670</v>
       </c>
       <c r="G70">
-        <v>0.865697261287618</v>
+        <v>0.6176702117567822</v>
       </c>
       <c r="H70">
-        <v>0.6728517211507835</v>
+        <v>0.5370026263967813</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3601,19 +3626,19 @@
         </is>
       </c>
       <c r="D71">
-        <v>-2.101004394857745</v>
+        <v>-2.907462985526728</v>
       </c>
       <c r="E71">
-        <v>7.808558695844056</v>
+        <v>7.011792006320775</v>
       </c>
       <c r="F71">
-        <v>709.96650231839</v>
+        <v>670</v>
       </c>
       <c r="G71">
-        <v>0.2690643019659904</v>
+        <v>0.4146533415289269</v>
       </c>
       <c r="H71">
-        <v>0.7879583727567683</v>
+        <v>0.6785284223042697</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3643,19 +3668,19 @@
         </is>
       </c>
       <c r="D72">
-        <v>-12.9188234340038</v>
+        <v>-13.97701641616748</v>
       </c>
       <c r="E72">
-        <v>7.808558695844055</v>
+        <v>7.493906236484419</v>
       </c>
       <c r="F72">
-        <v>709.9665023182499</v>
+        <v>670</v>
       </c>
       <c r="G72">
-        <v>1.654444044952825</v>
+        <v>1.865117600233607</v>
       </c>
       <c r="H72">
-        <v>0.4991143898054624</v>
+        <v>0.1252036891523737</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3685,19 +3710,19 @@
         </is>
       </c>
       <c r="D73">
-        <v>-8.812171913972321</v>
+        <v>-8.960131764749335</v>
       </c>
       <c r="E73">
-        <v>8.759091211443804</v>
+        <v>7.177949784907961</v>
       </c>
       <c r="F73">
-        <v>710.029798731883</v>
+        <v>670</v>
       </c>
       <c r="G73">
-        <v>1.00606006961763</v>
+        <v>1.248285657220466</v>
       </c>
       <c r="H73">
-        <v>0.6294588047685638</v>
+        <v>0.2548349987227957</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3727,19 +3752,19 @@
         </is>
       </c>
       <c r="D74">
-        <v>-15.18325148320844</v>
+        <v>-16.81862231089195</v>
       </c>
       <c r="E74">
-        <v>7.808558695844058</v>
+        <v>6.606692522133283</v>
       </c>
       <c r="F74">
-        <v>709.9665023177274</v>
+        <v>670</v>
       </c>
       <c r="G74">
-        <v>1.944437132974285</v>
+        <v>2.545694726150394</v>
       </c>
       <c r="H74">
-        <v>0.1044747150889134</v>
+        <v>0.02225785166979127</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3749,6 +3774,11 @@
       <c r="J74" t="inlineStr">
         <is>
           <t>SF_early</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -3769,19 +3799,19 @@
         </is>
       </c>
       <c r="D75">
-        <v>-22.15122452098918</v>
+        <v>-24.67759537581939</v>
       </c>
       <c r="E75">
-        <v>7.808558695844058</v>
+        <v>7.415416863736815</v>
       </c>
       <c r="F75">
-        <v>709.9665023177213</v>
+        <v>670</v>
       </c>
       <c r="G75">
-        <v>2.836787861091279</v>
+        <v>3.327877020171153</v>
       </c>
       <c r="H75">
-        <v>0.02812116475047447</v>
+        <v>0.004990343459747269</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3816,19 +3846,19 @@
         </is>
       </c>
       <c r="D76">
-        <v>-19.19139818188389</v>
+        <v>-21.51150172713786</v>
       </c>
       <c r="E76">
-        <v>8.759091211443808</v>
+        <v>6.813109751628511</v>
       </c>
       <c r="F76">
-        <v>710.0297987318488</v>
+        <v>670</v>
       </c>
       <c r="G76">
-        <v>2.191026182808806</v>
+        <v>3.15736902990533</v>
       </c>
       <c r="H76">
-        <v>0.08632252265765811</v>
+        <v>0.004990343459747269</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3838,6 +3868,11 @@
       <c r="J76" t="inlineStr">
         <is>
           <t>SF_advanced</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -3858,19 +3893,19 @@
         </is>
       </c>
       <c r="D77">
-        <v>-19.3992862574041</v>
+        <v>-27.44401252696147</v>
       </c>
       <c r="E77">
-        <v>7.808558695844061</v>
+        <v>7.324922121885722</v>
       </c>
       <c r="F77">
-        <v>709.9665023177273</v>
+        <v>670</v>
       </c>
       <c r="G77">
-        <v>2.484361969095392</v>
+        <v>3.746662704435184</v>
       </c>
       <c r="H77">
-        <v>0.01981174670961707</v>
+        <v>0.0003892858718442184</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3905,19 +3940,19 @@
         </is>
       </c>
       <c r="D78">
-        <v>-42.41194560587466</v>
+        <v>-43.93567091344216</v>
       </c>
       <c r="E78">
-        <v>7.808558695844061</v>
+        <v>7.685201435177596</v>
       </c>
       <c r="F78">
-        <v>709.9665023177213</v>
+        <v>670</v>
       </c>
       <c r="G78">
-        <v>5.431469142755821</v>
+        <v>5.716918584896773</v>
       </c>
       <c r="H78">
-        <v>4.610401534660611E-07</v>
+        <v>9.802900888955615E-08</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3952,19 +3987,19 @@
         </is>
       </c>
       <c r="D79">
-        <v>-36.09794040072105</v>
+        <v>-39.03454952609623</v>
       </c>
       <c r="E79">
-        <v>8.75909121144381</v>
+        <v>7.553879631416326</v>
       </c>
       <c r="F79">
-        <v>710.0297987317699</v>
+        <v>670</v>
       </c>
       <c r="G79">
-        <v>4.121196997418962</v>
+        <v>5.167483654856357</v>
       </c>
       <c r="H79">
-        <v>0.0001264175145939954</v>
+        <v>9.403463887316393E-07</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3999,19 +4034,19 @@
         </is>
       </c>
       <c r="D80">
-        <v>-18.10934698962698</v>
+        <v>-22.95842217679893</v>
       </c>
       <c r="E80">
-        <v>7.808558695844054</v>
+        <v>9.163769891839637</v>
       </c>
       <c r="F80">
-        <v>709.9665023183898</v>
+        <v>670</v>
       </c>
       <c r="G80">
-        <v>2.319166403816022</v>
+        <v>2.505346865730824</v>
       </c>
       <c r="H80">
-        <v>0.03100343229182026</v>
+        <v>0.01870395806807687</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4046,19 +4081,19 @@
         </is>
       </c>
       <c r="D81">
-        <v>-36.69600119877753</v>
+        <v>-39.10087558481381</v>
       </c>
       <c r="E81">
-        <v>7.808558695844054</v>
+        <v>10.34515428451811</v>
       </c>
       <c r="F81">
-        <v>709.9665023182501</v>
+        <v>670</v>
       </c>
       <c r="G81">
-        <v>4.699458969080712</v>
+        <v>3.779631942592645</v>
       </c>
       <c r="H81">
-        <v>1.880021643943613E-05</v>
+        <v>0.001026372622607854</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4093,19 +4128,19 @@
         </is>
       </c>
       <c r="D82">
-        <v>-25.24782338865833</v>
+        <v>-25.13094971007792</v>
       </c>
       <c r="E82">
-        <v>8.759091211443804</v>
+        <v>9.223653955597859</v>
       </c>
       <c r="F82">
-        <v>710.0297987316259</v>
+        <v>670</v>
       </c>
       <c r="G82">
-        <v>2.882470655822364</v>
+        <v>2.724619747342742</v>
       </c>
       <c r="H82">
-        <v>0.01219472145364635</v>
+        <v>0.01417596961095297</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4140,19 +4175,19 @@
         </is>
       </c>
       <c r="D83">
-        <v>-15.93251924321577</v>
+        <v>-23.41123398003711</v>
       </c>
       <c r="E83">
-        <v>7.808558695844058</v>
+        <v>11.18685675260856</v>
       </c>
       <c r="F83">
-        <v>709.9665023178007</v>
+        <v>670</v>
       </c>
       <c r="G83">
-        <v>2.04039181413793</v>
+        <v>2.092744592852506</v>
       </c>
       <c r="H83">
-        <v>0.0833616048338869</v>
+        <v>0.10768744763837</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4182,19 +4217,19 @@
         </is>
       </c>
       <c r="D84">
-        <v>-25.98888176588903</v>
+        <v>-24.92067345054431</v>
       </c>
       <c r="E84">
-        <v>7.808558695844058</v>
+        <v>12.03403285083768</v>
       </c>
       <c r="F84">
-        <v>709.9665023174193</v>
+        <v>670</v>
       </c>
       <c r="G84">
-        <v>3.328255927655519</v>
+        <v>2.070849710935399</v>
       </c>
       <c r="H84">
-        <v>0.00551402004811902</v>
+        <v>0.10768744763837</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4204,11 +4239,6 @@
       <c r="J84" t="inlineStr">
         <is>
           <t>SF_intermediate</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>*</t>
         </is>
       </c>
     </row>
@@ -4229,19 +4259,19 @@
         </is>
       </c>
       <c r="D85">
-        <v>-22.31399605336683</v>
+        <v>-21.43607299804163</v>
       </c>
       <c r="E85">
-        <v>8.759091211443808</v>
+        <v>11.0981966481736</v>
       </c>
       <c r="F85">
-        <v>710.0297987317177</v>
+        <v>670</v>
       </c>
       <c r="G85">
-        <v>2.547524111201565</v>
+        <v>1.931491545661998</v>
       </c>
       <c r="H85">
-        <v>0.03317620294391571</v>
+        <v>0.10768744763837</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4251,11 +4281,6 @@
       <c r="J85" t="inlineStr">
         <is>
           <t>SF_advanced</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>*</t>
         </is>
       </c>
     </row>
@@ -4276,19 +4301,19 @@
         </is>
       </c>
       <c r="D86">
-        <v>-13.18999411756846</v>
+        <v>-18.69908241651422</v>
       </c>
       <c r="E86">
-        <v>7.808558695844055</v>
+        <v>13.39665126811828</v>
       </c>
       <c r="F86">
-        <v>709.9665023187572</v>
+        <v>670</v>
       </c>
       <c r="G86">
-        <v>1.689171411951934</v>
+        <v>1.395802730269975</v>
       </c>
       <c r="H86">
-        <v>0.1610769555778289</v>
+        <v>0.2448543990780712</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4318,19 +4343,19 @@
         </is>
       </c>
       <c r="D87">
-        <v>-25.7781700747353</v>
+        <v>-28.324962944267</v>
       </c>
       <c r="E87">
-        <v>7.808558695844054</v>
+        <v>13.77989592392893</v>
       </c>
       <c r="F87">
-        <v>709.966502318453</v>
+        <v>670</v>
       </c>
       <c r="G87">
-        <v>3.301271217754335</v>
+        <v>2.055528075148987</v>
       </c>
       <c r="H87">
-        <v>0.006063794260631016</v>
+        <v>0.08043010274622042</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4340,11 +4365,6 @@
       <c r="J87" t="inlineStr">
         <is>
           <t>SF_intermediate</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>*</t>
         </is>
       </c>
     </row>
@@ -4365,19 +4385,19 @@
         </is>
       </c>
       <c r="D88">
-        <v>-4.63913286003937</v>
+        <v>-0.9864575800881781</v>
       </c>
       <c r="E88">
-        <v>8.759091211443804</v>
+        <v>12.98199170011837</v>
       </c>
       <c r="F88">
-        <v>710.0297987314395</v>
+        <v>670</v>
       </c>
       <c r="G88">
-        <v>0.5296363227703709</v>
+        <v>0.07598661306178336</v>
       </c>
       <c r="H88">
-        <v>0.5965296654075449</v>
+        <v>0.9394524319963988</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4407,19 +4427,19 @@
         </is>
       </c>
       <c r="D89">
-        <v>0.2245775773964786</v>
+        <v>-5.206020778669711</v>
       </c>
       <c r="E89">
-        <v>7.808558695844054</v>
+        <v>17.7301108773053</v>
       </c>
       <c r="F89">
-        <v>709.9665023179815</v>
+        <v>670</v>
       </c>
       <c r="G89">
-        <v>-0.02876043917246924</v>
+        <v>0.2936259572597182</v>
       </c>
       <c r="H89">
-        <v>0.9770637351884492</v>
+        <v>0.9229616024949449</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4449,19 +4469,19 @@
         </is>
       </c>
       <c r="D90">
-        <v>-31.35836647597246</v>
+        <v>-33.01622770619499</v>
       </c>
       <c r="E90">
-        <v>7.808558695844054</v>
+        <v>19.20308561149712</v>
       </c>
       <c r="F90">
-        <v>709.9665023175621</v>
+        <v>670</v>
       </c>
       <c r="G90">
-        <v>4.015896876418731</v>
+        <v>1.719318883129271</v>
       </c>
       <c r="H90">
-        <v>0.0001965850210583635</v>
+        <v>0.1720363747693364</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4471,11 +4491,6 @@
       <c r="J90" t="inlineStr">
         <is>
           <t>SF_intermediate</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>*</t>
         </is>
       </c>
     </row>
@@ -4496,19 +4511,19 @@
         </is>
       </c>
       <c r="D91">
-        <v>-8.064803012127845</v>
+        <v>-5.265435510965023</v>
       </c>
       <c r="E91">
-        <v>8.759091211443804</v>
+        <v>17.5451084706969</v>
       </c>
       <c r="F91">
-        <v>710.0297987313298</v>
+        <v>670</v>
       </c>
       <c r="G91">
-        <v>0.9207351330685005</v>
+        <v>0.3001084615554889</v>
       </c>
       <c r="H91">
-        <v>0.4290017343017434</v>
+        <v>0.9229616024949449</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
